--- a/ch_10/ch_10_solution.xlsx
+++ b/ch_10/ch_10_solution.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30103"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30501"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\georg\Documents\GitHub\Python-in-Excel-for-Data-Analytics\ch_10_excel_features\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\GeorgeMount\Documents\GitHub\Python-in-Excel-for-Data-Analytics\ch_10\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0BA2A0BC-9FCC-4973-8FA5-F4CAFCF7CD8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3C55664-438B-4492-935A-00658033E2BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-93" yWindow="-93" windowWidth="16826" windowHeight="11280" xr2:uid="{9C0D6B3D-BF38-4EC0-B560-276A782F5215}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="18915" windowHeight="12676" xr2:uid="{9C0D6B3D-BF38-4EC0-B560-276A782F5215}"/>
   </bookViews>
   <sheets>
     <sheet name="power-query" sheetId="3" r:id="rId1"/>
@@ -322,7 +322,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
@@ -331,6 +331,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2"/>
     <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="2" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1957,9 +1958,10 @@
     <tabColor theme="3" tint="0.249977111117893"/>
   </sheetPr>
   <dimension ref="A1:F239"/>
-  <sheetFormatPr defaultRowHeight="18.350000000000001"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="21.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.47265625" customWidth="1"/>
+    <col min="2" max="3" width="19" style="6" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
@@ -1967,10 +1969,10 @@
         <f t="array" ref="A1:F239">_xlfn._xlws.PY(0,0,_xlfn.PQSOURCE("0cb43bd8-b241-4ba9-ad35-48b4be168ad2"))</f>
         <v>Country or territory</v>
       </c>
-      <c r="B1" t="str">
+      <c r="B1" s="6" t="str">
         <v>Population(1 July 2022)</v>
       </c>
-      <c r="C1" t="str">
+      <c r="C1" s="6" t="str">
         <v>Population(1 July 2023)</v>
       </c>
       <c r="D1" t="str">
@@ -1987,10 +1989,10 @@
       <c r="A2" t="str">
         <v>World</v>
       </c>
-      <c r="B2">
+      <c r="B2" s="6">
         <v>8021407192</v>
       </c>
-      <c r="C2">
+      <c r="C2" s="6">
         <v>8091734930</v>
       </c>
       <c r="D2" t="str">
@@ -2007,10 +2009,10 @@
       <c r="A3" t="str">
         <v>India</v>
       </c>
-      <c r="B3">
+      <c r="B3" s="6">
         <v>1425423212</v>
       </c>
-      <c r="C3">
+      <c r="C3" s="6">
         <v>1438069596</v>
       </c>
       <c r="D3" t="str">
@@ -2027,10 +2029,10 @@
       <c r="A4" t="str">
         <v>China[a]</v>
       </c>
-      <c r="B4">
+      <c r="B4" s="6">
         <v>1425179569</v>
       </c>
-      <c r="C4">
+      <c r="C4" s="6">
         <v>1422584933</v>
       </c>
       <c r="D4" t="str">
@@ -2047,10 +2049,10 @@
       <c r="A5" t="str">
         <v>United States</v>
       </c>
-      <c r="B5">
+      <c r="B5" s="6">
         <v>341534046</v>
       </c>
-      <c r="C5">
+      <c r="C5" s="6">
         <v>343477335</v>
       </c>
       <c r="D5" t="str">
@@ -2067,10 +2069,10 @@
       <c r="A6" t="str">
         <v>Indonesia</v>
       </c>
-      <c r="B6">
+      <c r="B6" s="6">
         <v>278830529</v>
       </c>
-      <c r="C6">
+      <c r="C6" s="6">
         <v>281190067</v>
       </c>
       <c r="D6" t="str">
@@ -2087,10 +2089,10 @@
       <c r="A7" t="str">
         <v>Pakistan</v>
       </c>
-      <c r="B7">
+      <c r="B7" s="6">
         <v>243700667</v>
       </c>
-      <c r="C7">
+      <c r="C7" s="6">
         <v>247504495</v>
       </c>
       <c r="D7" t="str">
@@ -2107,10 +2109,10 @@
       <c r="A8" t="str">
         <v>Nigeria</v>
       </c>
-      <c r="B8">
+      <c r="B8" s="6">
         <v>223150896</v>
       </c>
-      <c r="C8">
+      <c r="C8" s="6">
         <v>227882945</v>
       </c>
       <c r="D8" t="str">
@@ -2127,10 +2129,10 @@
       <c r="A9" t="str">
         <v>Brazil</v>
       </c>
-      <c r="B9">
+      <c r="B9" s="6">
         <v>210306415</v>
       </c>
-      <c r="C9">
+      <c r="C9" s="6">
         <v>211140729</v>
       </c>
       <c r="D9" t="str">
@@ -2147,10 +2149,10 @@
       <c r="A10" t="str">
         <v>Bangladesh</v>
       </c>
-      <c r="B10">
+      <c r="B10" s="6">
         <v>169384897</v>
       </c>
-      <c r="C10">
+      <c r="C10" s="6">
         <v>171466990</v>
       </c>
       <c r="D10" t="str">
@@ -2167,10 +2169,10 @@
       <c r="A11" t="str">
         <v>Russia</v>
       </c>
-      <c r="B11">
+      <c r="B11" s="6">
         <v>145579899</v>
       </c>
-      <c r="C11">
+      <c r="C11" s="6">
         <v>145440500</v>
       </c>
       <c r="D11" t="str">
@@ -2187,10 +2189,10 @@
       <c r="A12" t="str">
         <v>Mexico</v>
       </c>
-      <c r="B12">
+      <c r="B12" s="6">
         <v>128613117</v>
       </c>
-      <c r="C12">
+      <c r="C12" s="6">
         <v>129739759</v>
       </c>
       <c r="D12" t="str">
@@ -2207,10 +2209,10 @@
       <c r="A13" t="str">
         <v>Ethiopia</v>
       </c>
-      <c r="B13">
+      <c r="B13" s="6">
         <v>125384287</v>
       </c>
-      <c r="C13">
+      <c r="C13" s="6">
         <v>128691692</v>
       </c>
       <c r="D13" t="str">
@@ -2227,10 +2229,10 @@
       <c r="A14" t="str">
         <v>Japan</v>
       </c>
-      <c r="B14">
+      <c r="B14" s="6">
         <v>124997578</v>
       </c>
-      <c r="C14">
+      <c r="C14" s="6">
         <v>124370947</v>
       </c>
       <c r="D14" t="str">
@@ -2247,10 +2249,10 @@
       <c r="A15" t="str">
         <v>Philippines</v>
       </c>
-      <c r="B15">
+      <c r="B15" s="6">
         <v>113964338</v>
       </c>
-      <c r="C15">
+      <c r="C15" s="6">
         <v>114891199</v>
       </c>
       <c r="D15" t="str">
@@ -2267,10 +2269,10 @@
       <c r="A16" t="str">
         <v>Egypt</v>
       </c>
-      <c r="B16">
+      <c r="B16" s="6">
         <v>112618250</v>
       </c>
-      <c r="C16">
+      <c r="C16" s="6">
         <v>114535772</v>
       </c>
       <c r="D16" t="str">
@@ -2287,10 +2289,10 @@
       <c r="A17" t="str">
         <v>DR Congo</v>
       </c>
-      <c r="B17">
+      <c r="B17" s="6">
         <v>102396968</v>
       </c>
-      <c r="C17">
+      <c r="C17" s="6">
         <v>105789731</v>
       </c>
       <c r="D17" t="str">
@@ -2307,10 +2309,10 @@
       <c r="A18" t="str">
         <v>Vietnam</v>
       </c>
-      <c r="B18">
+      <c r="B18" s="6">
         <v>99680655</v>
       </c>
-      <c r="C18">
+      <c r="C18" s="6">
         <v>100352192</v>
       </c>
       <c r="D18" t="str">
@@ -2327,10 +2329,10 @@
       <c r="A19" t="str">
         <v>Iran</v>
       </c>
-      <c r="B19">
+      <c r="B19" s="6">
         <v>89524246</v>
       </c>
-      <c r="C19">
+      <c r="C19" s="6">
         <v>90608707</v>
       </c>
       <c r="D19" t="str">
@@ -2347,10 +2349,10 @@
       <c r="A20" t="str">
         <v>Turkey</v>
       </c>
-      <c r="B20">
+      <c r="B20" s="6">
         <v>87058473</v>
       </c>
-      <c r="C20">
+      <c r="C20" s="6">
         <v>87270501</v>
       </c>
       <c r="D20" t="str">
@@ -2367,10 +2369,10 @@
       <c r="A21" t="str">
         <v>Germany</v>
       </c>
-      <c r="B21">
+      <c r="B21" s="6">
         <v>84086227</v>
       </c>
-      <c r="C21">
+      <c r="C21" s="6">
         <v>84548231</v>
       </c>
       <c r="D21" t="str">
@@ -2387,10 +2389,10 @@
       <c r="A22" t="str">
         <v>Thailand</v>
       </c>
-      <c r="B22">
+      <c r="B22" s="6">
         <v>71735329</v>
       </c>
-      <c r="C22">
+      <c r="C22" s="6">
         <v>71702435</v>
       </c>
       <c r="D22" t="str">
@@ -2407,10 +2409,10 @@
       <c r="A23" t="str">
         <v>United Kingdom</v>
       </c>
-      <c r="B23">
+      <c r="B23" s="6">
         <v>68179315</v>
       </c>
-      <c r="C23">
+      <c r="C23" s="6">
         <v>68682962</v>
       </c>
       <c r="D23" t="str">
@@ -2427,10 +2429,10 @@
       <c r="A24" t="str">
         <v>Tanzania[b]</v>
       </c>
-      <c r="B24">
+      <c r="B24" s="6">
         <v>64711821</v>
       </c>
-      <c r="C24">
+      <c r="C24" s="6">
         <v>66617606</v>
       </c>
       <c r="D24" t="str">
@@ -2447,10 +2449,10 @@
       <c r="A25" t="str">
         <v>France[c]</v>
       </c>
-      <c r="B25">
+      <c r="B25" s="6">
         <v>66277409</v>
       </c>
-      <c r="C25">
+      <c r="C25" s="6">
         <v>66438822</v>
       </c>
       <c r="D25" t="str">
@@ -2467,10 +2469,10 @@
       <c r="A26" t="str">
         <v>South Africa</v>
       </c>
-      <c r="B26">
+      <c r="B26" s="6">
         <v>62378410</v>
       </c>
-      <c r="C26">
+      <c r="C26" s="6">
         <v>63212384</v>
       </c>
       <c r="D26" t="str">
@@ -2487,10 +2489,10 @@
       <c r="A27" t="str">
         <v>Italy</v>
       </c>
-      <c r="B27">
+      <c r="B27" s="6">
         <v>59619115</v>
       </c>
-      <c r="C27">
+      <c r="C27" s="6">
         <v>59499453</v>
       </c>
       <c r="D27" t="str">
@@ -2507,10 +2509,10 @@
       <c r="A28" t="str">
         <v>Kenya</v>
       </c>
-      <c r="B28">
+      <c r="B28" s="6">
         <v>54252461</v>
       </c>
-      <c r="C28">
+      <c r="C28" s="6">
         <v>55339003</v>
       </c>
       <c r="D28" t="str">
@@ -2527,10 +2529,10 @@
       <c r="A29" t="str">
         <v>Myanmar</v>
       </c>
-      <c r="B29">
+      <c r="B29" s="6">
         <v>53756787</v>
       </c>
-      <c r="C29">
+      <c r="C29" s="6">
         <v>54133798</v>
       </c>
       <c r="D29" t="str">
@@ -2547,10 +2549,10 @@
       <c r="A30" t="str">
         <v>Colombia</v>
       </c>
-      <c r="B30">
+      <c r="B30" s="6">
         <v>51737944</v>
       </c>
-      <c r="C30">
+      <c r="C30" s="6">
         <v>52321152</v>
       </c>
       <c r="D30" t="str">
@@ -2567,10 +2569,10 @@
       <c r="A31" t="str">
         <v>South Korea</v>
       </c>
-      <c r="B31">
+      <c r="B31" s="6">
         <v>51782512</v>
       </c>
-      <c r="C31">
+      <c r="C31" s="6">
         <v>51748739</v>
       </c>
       <c r="D31" t="str">
@@ -2587,10 +2589,10 @@
       <c r="A32" t="str">
         <v>Sudan</v>
       </c>
-      <c r="B32">
+      <c r="B32" s="6">
         <v>49383346</v>
       </c>
-      <c r="C32">
+      <c r="C32" s="6">
         <v>50042791</v>
       </c>
       <c r="D32" t="str">
@@ -2607,10 +2609,10 @@
       <c r="A33" t="str">
         <v>Uganda</v>
       </c>
-      <c r="B33">
+      <c r="B33" s="6">
         <v>47312719</v>
       </c>
-      <c r="C33">
+      <c r="C33" s="6">
         <v>48656601</v>
       </c>
       <c r="D33" t="str">
@@ -2627,10 +2629,10 @@
       <c r="A34" t="str">
         <v>Spain[d]</v>
       </c>
-      <c r="B34">
+      <c r="B34" s="6">
         <v>47828382</v>
       </c>
-      <c r="C34">
+      <c r="C34" s="6">
         <v>47911579</v>
       </c>
       <c r="D34" t="str">
@@ -2647,10 +2649,10 @@
       <c r="A35" t="str">
         <v>Algeria</v>
       </c>
-      <c r="B35">
+      <c r="B35" s="6">
         <v>45477389</v>
       </c>
-      <c r="C35">
+      <c r="C35" s="6">
         <v>46164219</v>
       </c>
       <c r="D35" t="str">
@@ -2667,10 +2669,10 @@
       <c r="A36" t="str">
         <v>Argentina</v>
       </c>
-      <c r="B36">
+      <c r="B36" s="6">
         <v>45407904</v>
       </c>
-      <c r="C36">
+      <c r="C36" s="6">
         <v>45538401</v>
       </c>
       <c r="D36" t="str">
@@ -2687,10 +2689,10 @@
       <c r="A37" t="str">
         <v>Iraq</v>
       </c>
-      <c r="B37">
+      <c r="B37" s="6">
         <v>44070551</v>
       </c>
-      <c r="C37">
+      <c r="C37" s="6">
         <v>45074049</v>
       </c>
       <c r="D37" t="str">
@@ -2707,10 +2709,10 @@
       <c r="A38" t="str">
         <v>Afghanistan</v>
       </c>
-      <c r="B38">
+      <c r="B38" s="6">
         <v>40578842</v>
       </c>
-      <c r="C38">
+      <c r="C38" s="6">
         <v>41454761</v>
       </c>
       <c r="D38" t="str">
@@ -2727,10 +2729,10 @@
       <c r="A39" t="str">
         <v>Yemen</v>
       </c>
-      <c r="B39">
+      <c r="B39" s="6">
         <v>38222876</v>
       </c>
-      <c r="C39">
+      <c r="C39" s="6">
         <v>39390799</v>
       </c>
       <c r="D39" t="str">
@@ -2747,10 +2749,10 @@
       <c r="A40" t="str">
         <v>Canada</v>
       </c>
-      <c r="B40">
+      <c r="B40" s="6">
         <v>38821259</v>
       </c>
-      <c r="C40">
+      <c r="C40" s="6">
         <v>39299105</v>
       </c>
       <c r="D40" t="str">
@@ -2767,10 +2769,10 @@
       <c r="A41" t="str">
         <v>Poland</v>
       </c>
-      <c r="B41">
+      <c r="B41" s="6">
         <v>38385739</v>
       </c>
-      <c r="C41">
+      <c r="C41" s="6">
         <v>38762844</v>
       </c>
       <c r="D41" t="str">
@@ -2787,10 +2789,10 @@
       <c r="A42" t="str">
         <v>Ukraine[e]</v>
       </c>
-      <c r="B42">
+      <c r="B42" s="6">
         <v>41048766</v>
       </c>
-      <c r="C42">
+      <c r="C42" s="6">
         <v>37732836</v>
       </c>
       <c r="D42" t="str">
@@ -2807,10 +2809,10 @@
       <c r="A43" t="str">
         <v>Morocco</v>
       </c>
-      <c r="B43">
+      <c r="B43" s="6">
         <v>37329064</v>
       </c>
-      <c r="C43">
+      <c r="C43" s="6">
         <v>37712505</v>
       </c>
       <c r="D43" t="str">
@@ -2827,10 +2829,10 @@
       <c r="A44" t="str">
         <v>Angola</v>
       </c>
-      <c r="B44">
+      <c r="B44" s="6">
         <v>35635029</v>
       </c>
-      <c r="C44">
+      <c r="C44" s="6">
         <v>36749906</v>
       </c>
       <c r="D44" t="str">
@@ -2847,10 +2849,10 @@
       <c r="A45" t="str">
         <v>Uzbekistan</v>
       </c>
-      <c r="B45">
+      <c r="B45" s="6">
         <v>34938955</v>
       </c>
-      <c r="C45">
+      <c r="C45" s="6">
         <v>35652307</v>
       </c>
       <c r="D45" t="str">
@@ -2867,10 +2869,10 @@
       <c r="A46" t="str">
         <v>Malaysia</v>
       </c>
-      <c r="B46">
+      <c r="B46" s="6">
         <v>34695493</v>
       </c>
-      <c r="C46">
+      <c r="C46" s="6">
         <v>35126298</v>
       </c>
       <c r="D46" t="str">
@@ -2887,10 +2889,10 @@
       <c r="A47" t="str">
         <v>Peru</v>
       </c>
-      <c r="B47">
+      <c r="B47" s="6">
         <v>33475438</v>
       </c>
-      <c r="C47">
+      <c r="C47" s="6">
         <v>33845617</v>
       </c>
       <c r="D47" t="str">
@@ -2907,10 +2909,10 @@
       <c r="A48" t="str">
         <v>Ghana</v>
       </c>
-      <c r="B48">
+      <c r="B48" s="6">
         <v>33149152</v>
       </c>
-      <c r="C48">
+      <c r="C48" s="6">
         <v>33787914</v>
       </c>
       <c r="D48" t="str">
@@ -2927,10 +2929,10 @@
       <c r="A49" t="str">
         <v>Mozambique</v>
       </c>
-      <c r="B49">
+      <c r="B49" s="6">
         <v>32656246</v>
       </c>
-      <c r="C49">
+      <c r="C49" s="6">
         <v>33635160</v>
       </c>
       <c r="D49" t="str">
@@ -2947,10 +2949,10 @@
       <c r="A50" t="str">
         <v>Saudi Arabia</v>
       </c>
-      <c r="B50">
+      <c r="B50" s="6">
         <v>32175352</v>
       </c>
-      <c r="C50">
+      <c r="C50" s="6">
         <v>32264292</v>
       </c>
       <c r="D50" t="str">
@@ -2967,10 +2969,10 @@
       <c r="A51" t="str">
         <v>Madagascar</v>
       </c>
-      <c r="B51">
+      <c r="B51" s="6">
         <v>30437261</v>
       </c>
-      <c r="C51">
+      <c r="C51" s="6">
         <v>31195932</v>
       </c>
       <c r="D51" t="str">
@@ -2987,10 +2989,10 @@
       <c r="A52" t="str">
         <v>Ivory Coast</v>
       </c>
-      <c r="B52">
+      <c r="B52" s="6">
         <v>30395002</v>
       </c>
-      <c r="C52">
+      <c r="C52" s="6">
         <v>31165654</v>
       </c>
       <c r="D52" t="str">
@@ -3007,10 +3009,10 @@
       <c r="A53" t="str">
         <v>Nepal</v>
       </c>
-      <c r="B53">
+      <c r="B53" s="6">
         <v>29715436</v>
       </c>
-      <c r="C53">
+      <c r="C53" s="6">
         <v>29964614</v>
       </c>
       <c r="D53" t="str">
@@ -3027,10 +3029,10 @@
       <c r="A54" t="str">
         <v>Cameroon</v>
       </c>
-      <c r="B54">
+      <c r="B54" s="6">
         <v>27632771</v>
       </c>
-      <c r="C54">
+      <c r="C54" s="6">
         <v>28372687</v>
       </c>
       <c r="D54" t="str">
@@ -3047,10 +3049,10 @@
       <c r="A55" t="str">
         <v>Venezuela</v>
       </c>
-      <c r="B55">
+      <c r="B55" s="6">
         <v>28213017</v>
       </c>
-      <c r="C55">
+      <c r="C55" s="6">
         <v>28300854</v>
       </c>
       <c r="D55" t="str">
@@ -3067,10 +3069,10 @@
       <c r="A56" t="str">
         <v>Australia[f]</v>
       </c>
-      <c r="B56">
+      <c r="B56" s="6">
         <v>26200984</v>
       </c>
-      <c r="C56">
+      <c r="C56" s="6">
         <v>26451124</v>
       </c>
       <c r="D56" t="str">
@@ -3087,10 +3089,10 @@
       <c r="A57" t="str">
         <v>North Korea</v>
       </c>
-      <c r="B57">
+      <c r="B57" s="6">
         <v>26329845</v>
       </c>
-      <c r="C57">
+      <c r="C57" s="6">
         <v>26418204</v>
       </c>
       <c r="D57" t="str">
@@ -3107,10 +3109,10 @@
       <c r="A58" t="str">
         <v>Niger</v>
       </c>
-      <c r="B58">
+      <c r="B58" s="6">
         <v>25311973</v>
       </c>
-      <c r="C58">
+      <c r="C58" s="6">
         <v>26159867</v>
       </c>
       <c r="D58" t="str">
@@ -3127,10 +3129,10 @@
       <c r="A59" t="str">
         <v>Mali</v>
       </c>
-      <c r="B59">
+      <c r="B59" s="6">
         <v>23072640</v>
       </c>
-      <c r="C59">
+      <c r="C59" s="6">
         <v>23769127</v>
       </c>
       <c r="D59" t="str">
@@ -3147,10 +3149,10 @@
       <c r="A60" t="str">
         <v>Syria</v>
       </c>
-      <c r="B60">
+      <c r="B60" s="6">
         <v>22462173</v>
       </c>
-      <c r="C60">
+      <c r="C60" s="6">
         <v>23594623</v>
       </c>
       <c r="D60" t="str">
@@ -3167,10 +3169,10 @@
       <c r="A61" t="str">
         <v>Taiwan[g]</v>
       </c>
-      <c r="B61">
+      <c r="B61" s="6">
         <v>23420111</v>
       </c>
-      <c r="C61">
+      <c r="C61" s="6">
         <v>23317145</v>
       </c>
       <c r="D61" t="str">
@@ -3187,10 +3189,10 @@
       <c r="A62" t="str">
         <v>Burkina Faso</v>
       </c>
-      <c r="B62">
+      <c r="B62" s="6">
         <v>22509038</v>
       </c>
-      <c r="C62">
+      <c r="C62" s="6">
         <v>23025776</v>
       </c>
       <c r="D62" t="str">
@@ -3207,10 +3209,10 @@
       <c r="A63" t="str">
         <v>Sri Lanka</v>
       </c>
-      <c r="B63">
+      <c r="B63" s="6">
         <v>22834965</v>
       </c>
-      <c r="C63">
+      <c r="C63" s="6">
         <v>22971617</v>
       </c>
       <c r="D63" t="str">
@@ -3227,10 +3229,10 @@
       <c r="A64" t="str">
         <v>Malawi</v>
       </c>
-      <c r="B64">
+      <c r="B64" s="6">
         <v>20568728</v>
       </c>
-      <c r="C64">
+      <c r="C64" s="6">
         <v>21104482</v>
       </c>
       <c r="D64" t="str">
@@ -3247,10 +3249,10 @@
       <c r="A65" t="str">
         <v>Zambia</v>
       </c>
-      <c r="B65">
+      <c r="B65" s="6">
         <v>20152938</v>
       </c>
-      <c r="C65">
+      <c r="C65" s="6">
         <v>20723965</v>
       </c>
       <c r="D65" t="str">
@@ -3267,10 +3269,10 @@
       <c r="A66" t="str">
         <v>Kazakhstan</v>
       </c>
-      <c r="B66">
+      <c r="B66" s="6">
         <v>20034609</v>
       </c>
-      <c r="C66">
+      <c r="C66" s="6">
         <v>20330104</v>
       </c>
       <c r="D66" t="str">
@@ -3287,10 +3289,10 @@
       <c r="A67" t="str">
         <v>Chile</v>
       </c>
-      <c r="B67">
+      <c r="B67" s="6">
         <v>19553036</v>
       </c>
-      <c r="C67">
+      <c r="C67" s="6">
         <v>19658835</v>
       </c>
       <c r="D67" t="str">
@@ -3307,10 +3309,10 @@
       <c r="A68" t="str">
         <v>Chad</v>
       </c>
-      <c r="B68">
+      <c r="B68" s="6">
         <v>18455316</v>
       </c>
-      <c r="C68">
+      <c r="C68" s="6">
         <v>19319064</v>
       </c>
       <c r="D68" t="str">
@@ -3327,10 +3329,10 @@
       <c r="A69" t="str">
         <v>Romania</v>
       </c>
-      <c r="B69">
+      <c r="B69" s="6">
         <v>19166772</v>
       </c>
-      <c r="C69">
+      <c r="C69" s="6">
         <v>19118479</v>
       </c>
       <c r="D69" t="str">
@@ -3347,10 +3349,10 @@
       <c r="A70" t="str">
         <v>Somalia[h]</v>
       </c>
-      <c r="B70">
+      <c r="B70" s="6">
         <v>17801897</v>
       </c>
-      <c r="C70">
+      <c r="C70" s="6">
         <v>18358615</v>
       </c>
       <c r="D70" t="str">
@@ -3367,10 +3369,10 @@
       <c r="A71" t="str">
         <v>Guatemala</v>
       </c>
-      <c r="B71">
+      <c r="B71" s="6">
         <v>17847877</v>
       </c>
-      <c r="C71">
+      <c r="C71" s="6">
         <v>18124838</v>
       </c>
       <c r="D71" t="str">
@@ -3387,10 +3389,10 @@
       <c r="A72" t="str">
         <v>Senegal</v>
       </c>
-      <c r="B72">
+      <c r="B72" s="6">
         <v>17651103</v>
       </c>
-      <c r="C72">
+      <c r="C72" s="6">
         <v>18077573</v>
       </c>
       <c r="D72" t="str">
@@ -3407,10 +3409,10 @@
       <c r="A73" t="str">
         <v>Netherlands[i]</v>
       </c>
-      <c r="B73">
+      <c r="B73" s="6">
         <v>17904421</v>
       </c>
-      <c r="C73">
+      <c r="C73" s="6">
         <v>18092524</v>
       </c>
       <c r="D73" t="str">
@@ -3427,10 +3429,10 @@
       <c r="A74" t="str">
         <v>Ecuador</v>
       </c>
-      <c r="B74">
+      <c r="B74" s="6">
         <v>17823897</v>
       </c>
-      <c r="C74">
+      <c r="C74" s="6">
         <v>17980083</v>
       </c>
       <c r="D74" t="str">
@@ -3447,10 +3449,10 @@
       <c r="A75" t="str">
         <v>Cambodia</v>
       </c>
-      <c r="B75">
+      <c r="B75" s="6">
         <v>17201724</v>
       </c>
-      <c r="C75">
+      <c r="C75" s="6">
         <v>17423880</v>
       </c>
       <c r="D75" t="str">
@@ -3467,10 +3469,10 @@
       <c r="A76" t="str">
         <v>Zimbabwe</v>
       </c>
-      <c r="B76">
+      <c r="B76" s="6">
         <v>16069056</v>
       </c>
-      <c r="C76">
+      <c r="C76" s="6">
         <v>16340822</v>
       </c>
       <c r="D76" t="str">
@@ -3487,10 +3489,10 @@
       <c r="A77" t="str">
         <v>Guinea</v>
       </c>
-      <c r="B77">
+      <c r="B77" s="6">
         <v>14055137</v>
       </c>
-      <c r="C77">
+      <c r="C77" s="6">
         <v>14405465</v>
       </c>
       <c r="D77" t="str">
@@ -3507,10 +3509,10 @@
       <c r="A78" t="str">
         <v>Benin</v>
       </c>
-      <c r="B78">
+      <c r="B78" s="6">
         <v>13759501</v>
       </c>
-      <c r="C78">
+      <c r="C78" s="6">
         <v>14111034</v>
       </c>
       <c r="D78" t="str">
@@ -3527,10 +3529,10 @@
       <c r="A79" t="str">
         <v>Rwanda</v>
       </c>
-      <c r="B79">
+      <c r="B79" s="6">
         <v>13651030</v>
       </c>
-      <c r="C79">
+      <c r="C79" s="6">
         <v>13954471</v>
       </c>
       <c r="D79" t="str">
@@ -3547,10 +3549,10 @@
       <c r="A80" t="str">
         <v>Burundi</v>
       </c>
-      <c r="B80">
+      <c r="B80" s="6">
         <v>13321097</v>
       </c>
-      <c r="C80">
+      <c r="C80" s="6">
         <v>13689450</v>
       </c>
       <c r="D80" t="str">
@@ -3567,10 +3569,10 @@
       <c r="A81" t="str">
         <v>Bolivia</v>
       </c>
-      <c r="B81">
+      <c r="B81" s="6">
         <v>12077154</v>
       </c>
-      <c r="C81">
+      <c r="C81" s="6">
         <v>12244159</v>
       </c>
       <c r="D81" t="str">
@@ -3587,10 +3589,10 @@
       <c r="A82" t="str">
         <v>Tunisia</v>
       </c>
-      <c r="B82">
+      <c r="B82" s="6">
         <v>12119334</v>
       </c>
-      <c r="C82">
+      <c r="C82" s="6">
         <v>12200431</v>
       </c>
       <c r="D82" t="str">
@@ -3607,10 +3609,10 @@
       <c r="A83" t="str">
         <v>Belgium</v>
       </c>
-      <c r="B83">
+      <c r="B83" s="6">
         <v>11641820</v>
       </c>
-      <c r="C83">
+      <c r="C83" s="6">
         <v>11712893</v>
       </c>
       <c r="D83" t="str">
@@ -3627,10 +3629,10 @@
       <c r="A84" t="str">
         <v>Haiti</v>
       </c>
-      <c r="B84">
+      <c r="B84" s="6">
         <v>11503606</v>
       </c>
-      <c r="C84">
+      <c r="C84" s="6">
         <v>11637398</v>
       </c>
       <c r="D84" t="str">
@@ -3647,10 +3649,10 @@
       <c r="A85" t="str">
         <v>South Sudan</v>
       </c>
-      <c r="B85">
+      <c r="B85" s="6">
         <v>11021177</v>
       </c>
-      <c r="C85">
+      <c r="C85" s="6">
         <v>11483374</v>
       </c>
       <c r="D85" t="str">
@@ -3667,10 +3669,10 @@
       <c r="A86" t="str">
         <v>Jordan</v>
       </c>
-      <c r="B86">
+      <c r="B86" s="6">
         <v>11256263</v>
       </c>
-      <c r="C86">
+      <c r="C86" s="6">
         <v>11439213</v>
       </c>
       <c r="D86" t="str">
@@ -3687,10 +3689,10 @@
       <c r="A87" t="str">
         <v>Dominican Republic</v>
       </c>
-      <c r="B87">
+      <c r="B87" s="6">
         <v>11230734</v>
       </c>
-      <c r="C87">
+      <c r="C87" s="6">
         <v>11331265</v>
       </c>
       <c r="D87" t="str">
@@ -3707,10 +3709,10 @@
       <c r="A88" t="str">
         <v>Cuba</v>
       </c>
-      <c r="B88">
+      <c r="B88" s="6">
         <v>11059820</v>
       </c>
-      <c r="C88">
+      <c r="C88" s="6">
         <v>11019931</v>
       </c>
       <c r="D88" t="str">
@@ -3727,10 +3729,10 @@
       <c r="A89" t="str">
         <v>Czechia</v>
       </c>
-      <c r="B89">
+      <c r="B89" s="6">
         <v>10673213</v>
       </c>
-      <c r="C89">
+      <c r="C89" s="6">
         <v>10809716</v>
       </c>
       <c r="D89" t="str">
@@ -3747,10 +3749,10 @@
       <c r="A90" t="str">
         <v>Honduras</v>
       </c>
-      <c r="B90">
+      <c r="B90" s="6">
         <v>10463872</v>
       </c>
-      <c r="C90">
+      <c r="C90" s="6">
         <v>10644851</v>
       </c>
       <c r="D90" t="str">
@@ -3767,10 +3769,10 @@
       <c r="A91" t="str">
         <v>United Arab Emirates</v>
       </c>
-      <c r="B91">
+      <c r="B91" s="6">
         <v>10242086</v>
       </c>
-      <c r="C91">
+      <c r="C91" s="6">
         <v>10642081</v>
       </c>
       <c r="D91" t="str">
@@ -3787,10 +3789,10 @@
       <c r="A92" t="str">
         <v>Sweden</v>
       </c>
-      <c r="B92">
+      <c r="B92" s="6">
         <v>10487338</v>
       </c>
-      <c r="C92">
+      <c r="C92" s="6">
         <v>10551494</v>
       </c>
       <c r="D92" t="str">
@@ -3807,10 +3809,10 @@
       <c r="A93" t="str">
         <v>Portugal[j]</v>
       </c>
-      <c r="B93">
+      <c r="B93" s="6">
         <v>10417073</v>
       </c>
-      <c r="C93">
+      <c r="C93" s="6">
         <v>10430738</v>
       </c>
       <c r="D93" t="str">
@@ -3827,10 +3829,10 @@
       <c r="A94" t="str">
         <v>Tajikistan</v>
       </c>
-      <c r="B94">
+      <c r="B94" s="6">
         <v>10182222</v>
       </c>
-      <c r="C94">
+      <c r="C94" s="6">
         <v>10389799</v>
       </c>
       <c r="D94" t="str">
@@ -3847,10 +3849,10 @@
       <c r="A95" t="str">
         <v>Papua New Guinea</v>
       </c>
-      <c r="B95">
+      <c r="B95" s="6">
         <v>10203169</v>
       </c>
-      <c r="C95">
+      <c r="C95" s="6">
         <v>10389635</v>
       </c>
       <c r="D95" t="str">
@@ -3867,10 +3869,10 @@
       <c r="A96" t="str">
         <v>Azerbaijan</v>
       </c>
-      <c r="B96">
+      <c r="B96" s="6">
         <v>10295304</v>
       </c>
-      <c r="C96">
+      <c r="C96" s="6">
         <v>10318207</v>
       </c>
       <c r="D96" t="str">
@@ -3887,10 +3889,10 @@
       <c r="A97" t="str">
         <v>Greece</v>
       </c>
-      <c r="B97">
+      <c r="B97" s="6">
         <v>10412480</v>
       </c>
-      <c r="C97">
+      <c r="C97" s="6">
         <v>10242908</v>
       </c>
       <c r="D97" t="str">
@@ -3907,10 +3909,10 @@
       <c r="A98" t="str">
         <v>Hungary</v>
       </c>
-      <c r="B98">
+      <c r="B98" s="6">
         <v>9964306</v>
       </c>
-      <c r="C98">
+      <c r="C98" s="6">
         <v>9686463</v>
       </c>
       <c r="D98" t="str">
@@ -3927,10 +3929,10 @@
       <c r="A99" t="str">
         <v>Togo</v>
       </c>
-      <c r="B99">
+      <c r="B99" s="6">
         <v>9089738</v>
       </c>
-      <c r="C99">
+      <c r="C99" s="6">
         <v>9304337</v>
       </c>
       <c r="D99" t="str">
@@ -3947,10 +3949,10 @@
       <c r="A100" t="str">
         <v>Israel</v>
       </c>
-      <c r="B100">
+      <c r="B100" s="6">
         <v>9103151</v>
       </c>
-      <c r="C100">
+      <c r="C100" s="6">
         <v>9256314</v>
       </c>
       <c r="D100" t="str">
@@ -3967,10 +3969,10 @@
       <c r="A101" t="str">
         <v>Austria</v>
       </c>
-      <c r="B101">
+      <c r="B101" s="6">
         <v>9064677</v>
       </c>
-      <c r="C101">
+      <c r="C101" s="6">
         <v>9130429</v>
       </c>
       <c r="D101" t="str">
@@ -3987,10 +3989,10 @@
       <c r="A102" t="str">
         <v>Belarus</v>
       </c>
-      <c r="B102">
+      <c r="B102" s="6">
         <v>9173237</v>
       </c>
-      <c r="C102">
+      <c r="C102" s="6">
         <v>9115680</v>
       </c>
       <c r="D102" t="str">
@@ -4007,10 +4009,10 @@
       <c r="A103" t="str">
         <v>Switzerland</v>
       </c>
-      <c r="B103">
+      <c r="B103" s="6">
         <v>8792182</v>
       </c>
-      <c r="C103">
+      <c r="C103" s="6">
         <v>8870561</v>
       </c>
       <c r="D103" t="str">
@@ -4027,10 +4029,10 @@
       <c r="A104" t="str">
         <v>Sierra Leone</v>
       </c>
-      <c r="B104">
+      <c r="B104" s="6">
         <v>8276807</v>
       </c>
-      <c r="C104">
+      <c r="C104" s="6">
         <v>8460512</v>
       </c>
       <c r="D104" t="str">
@@ -4047,10 +4049,10 @@
       <c r="A105" t="str">
         <v>Laos</v>
       </c>
-      <c r="B105">
+      <c r="B105" s="6">
         <v>7559007</v>
       </c>
-      <c r="C105">
+      <c r="C105" s="6">
         <v>7664993</v>
       </c>
       <c r="D105" t="str">
@@ -4067,10 +4069,10 @@
       <c r="A106" t="str">
         <v>Hong Kong (China)[k]</v>
       </c>
-      <c r="B106">
+      <c r="B106" s="6">
         <v>7465915</v>
       </c>
-      <c r="C106">
+      <c r="C106" s="6">
         <v>7442734</v>
       </c>
       <c r="D106" t="str">
@@ -4087,10 +4089,10 @@
       <c r="A107" t="str">
         <v>Turkmenistan</v>
       </c>
-      <c r="B107">
+      <c r="B107" s="6">
         <v>7230193</v>
       </c>
-      <c r="C107">
+      <c r="C107" s="6">
         <v>7364438</v>
       </c>
       <c r="D107" t="str">
@@ -4107,10 +4109,10 @@
       <c r="A108" t="str">
         <v>Libya</v>
       </c>
-      <c r="B108">
+      <c r="B108" s="6">
         <v>7223805</v>
       </c>
-      <c r="C108">
+      <c r="C108" s="6">
         <v>7305659</v>
       </c>
       <c r="D108" t="str">
@@ -4127,10 +4129,10 @@
       <c r="A109" t="str">
         <v>Kyrgyzstan</v>
       </c>
-      <c r="B109">
+      <c r="B109" s="6">
         <v>6955788</v>
       </c>
-      <c r="C109">
+      <c r="C109" s="6">
         <v>7073516</v>
       </c>
       <c r="D109" t="str">
@@ -4147,10 +4149,10 @@
       <c r="A110" t="str">
         <v>Paraguay</v>
       </c>
-      <c r="B110">
+      <c r="B110" s="6">
         <v>6760464</v>
       </c>
-      <c r="C110">
+      <c r="C110" s="6">
         <v>6844146</v>
       </c>
       <c r="D110" t="str">
@@ -4167,10 +4169,10 @@
       <c r="A111" t="str">
         <v>Nicaragua</v>
       </c>
-      <c r="B111">
+      <c r="B111" s="6">
         <v>6730654</v>
       </c>
-      <c r="C111">
+      <c r="C111" s="6">
         <v>6823613</v>
       </c>
       <c r="D111" t="str">
@@ -4187,10 +4189,10 @@
       <c r="A112" t="str">
         <v>Bulgaria</v>
       </c>
-      <c r="B112">
+      <c r="B112" s="6">
         <v>6825864</v>
       </c>
-      <c r="C112">
+      <c r="C112" s="6">
         <v>6795803</v>
       </c>
       <c r="D112" t="str">
@@ -4207,10 +4209,10 @@
       <c r="A113" t="str">
         <v>Serbia[l]</v>
       </c>
-      <c r="B113">
+      <c r="B113" s="6">
         <v>6791213</v>
       </c>
-      <c r="C113">
+      <c r="C113" s="6">
         <v>6773201</v>
       </c>
       <c r="D113" t="str">
@@ -4227,10 +4229,10 @@
       <c r="A114" t="str">
         <v>El Salvador</v>
       </c>
-      <c r="B114">
+      <c r="B114" s="6">
         <v>6280319</v>
       </c>
-      <c r="C114">
+      <c r="C114" s="6">
         <v>6309624</v>
       </c>
       <c r="D114" t="str">
@@ -4247,10 +4249,10 @@
       <c r="A115" t="str">
         <v>Congo</v>
       </c>
-      <c r="B115">
+      <c r="B115" s="6">
         <v>6035104</v>
       </c>
-      <c r="C115">
+      <c r="C115" s="6">
         <v>6182885</v>
       </c>
       <c r="D115" t="str">
@@ -4267,10 +4269,10 @@
       <c r="A116" t="str">
         <v>Denmark</v>
       </c>
-      <c r="B116">
+      <c r="B116" s="6">
         <v>5902904</v>
       </c>
-      <c r="C116">
+      <c r="C116" s="6">
         <v>5948136</v>
       </c>
       <c r="D116" t="str">
@@ -4287,10 +4289,10 @@
       <c r="A117" t="str">
         <v>Singapore</v>
       </c>
-      <c r="B117">
+      <c r="B117" s="6">
         <v>5649885</v>
       </c>
-      <c r="C117">
+      <c r="C117" s="6">
         <v>5789090</v>
       </c>
       <c r="D117" t="str">
@@ -4307,10 +4309,10 @@
       <c r="A118" t="str">
         <v>Lebanon</v>
       </c>
-      <c r="B118">
+      <c r="B118" s="6">
         <v>5744489</v>
       </c>
-      <c r="C118">
+      <c r="C118" s="6">
         <v>5733493</v>
       </c>
       <c r="D118" t="str">
@@ -4327,10 +4329,10 @@
       <c r="A119" t="str">
         <v>Finland[m]</v>
       </c>
-      <c r="B119">
+      <c r="B119" s="6">
         <v>5569299</v>
       </c>
-      <c r="C119">
+      <c r="C119" s="6">
         <v>5601185</v>
       </c>
       <c r="D119" t="str">
@@ -4347,10 +4349,10 @@
       <c r="A120" t="str">
         <v>Norway[n]</v>
       </c>
-      <c r="B120">
+      <c r="B120" s="6">
         <v>5457801</v>
       </c>
-      <c r="C120">
+      <c r="C120" s="6">
         <v>5519167</v>
       </c>
       <c r="D120" t="str">
@@ -4367,10 +4369,10 @@
       <c r="A121" t="str">
         <v>Slovakia</v>
       </c>
-      <c r="B121">
+      <c r="B121" s="6">
         <v>5473197</v>
       </c>
-      <c r="C121">
+      <c r="C121" s="6">
         <v>5518055</v>
       </c>
       <c r="D121" t="str">
@@ -4387,10 +4389,10 @@
       <c r="A122" t="str">
         <v>Liberia</v>
       </c>
-      <c r="B122">
+      <c r="B122" s="6">
         <v>5373294</v>
       </c>
-      <c r="C122">
+      <c r="C122" s="6">
         <v>5493031</v>
       </c>
       <c r="D122" t="str">
@@ -4407,10 +4409,10 @@
       <c r="A123" t="str">
         <v>Palestine[o]</v>
       </c>
-      <c r="B123">
+      <c r="B123" s="6">
         <v>5305270</v>
       </c>
-      <c r="C123">
+      <c r="C123" s="6">
         <v>5409202</v>
       </c>
       <c r="D123" t="str">
@@ -4427,10 +4429,10 @@
       <c r="A124" t="str">
         <v>Ireland</v>
       </c>
-      <c r="B124">
+      <c r="B124" s="6">
         <v>5110016</v>
       </c>
-      <c r="C124">
+      <c r="C124" s="6">
         <v>5196630</v>
       </c>
       <c r="D124" t="str">
@@ -4447,10 +4449,10 @@
       <c r="A125" t="str">
         <v>New Zealand</v>
       </c>
-      <c r="B125">
+      <c r="B125" s="6">
         <v>5131734</v>
       </c>
-      <c r="C125">
+      <c r="C125" s="6">
         <v>5172836</v>
       </c>
       <c r="D125" t="str">
@@ -4467,10 +4469,10 @@
       <c r="A126" t="str">
         <v>Central African Republic</v>
       </c>
-      <c r="B126">
+      <c r="B126" s="6">
         <v>5098039</v>
       </c>
-      <c r="C126">
+      <c r="C126" s="6">
         <v>5152421</v>
       </c>
       <c r="D126" t="str">
@@ -4487,10 +4489,10 @@
       <c r="A127" t="str">
         <v>Costa Rica</v>
       </c>
-      <c r="B127">
+      <c r="B127" s="6">
         <v>5081765</v>
       </c>
-      <c r="C127">
+      <c r="C127" s="6">
         <v>5105525</v>
       </c>
       <c r="D127" t="str">
@@ -4507,10 +4509,10 @@
       <c r="A128" t="str">
         <v>Oman</v>
       </c>
-      <c r="B128">
+      <c r="B128" s="6">
         <v>4730226</v>
       </c>
-      <c r="C128">
+      <c r="C128" s="6">
         <v>5049269</v>
       </c>
       <c r="D128" t="str">
@@ -4527,10 +4529,10 @@
       <c r="A129" t="str">
         <v>Mauritania</v>
       </c>
-      <c r="B129">
+      <c r="B129" s="6">
         <v>4875637</v>
       </c>
-      <c r="C129">
+      <c r="C129" s="6">
         <v>5022441</v>
       </c>
       <c r="D129" t="str">
@@ -4547,10 +4549,10 @@
       <c r="A130" t="str">
         <v>Kuwait</v>
       </c>
-      <c r="B130">
+      <c r="B130" s="6">
         <v>4589511</v>
       </c>
-      <c r="C130">
+      <c r="C130" s="6">
         <v>4838782</v>
       </c>
       <c r="D130" t="str">
@@ -4567,10 +4569,10 @@
       <c r="A131" t="str">
         <v>Panama</v>
       </c>
-      <c r="B131">
+      <c r="B131" s="6">
         <v>4400773</v>
       </c>
-      <c r="C131">
+      <c r="C131" s="6">
         <v>4458759</v>
       </c>
       <c r="D131" t="str">
@@ -4587,10 +4589,10 @@
       <c r="A132" t="str">
         <v>Croatia</v>
       </c>
-      <c r="B132">
+      <c r="B132" s="6">
         <v>3907027</v>
       </c>
-      <c r="C132">
+      <c r="C132" s="6">
         <v>3896023</v>
       </c>
       <c r="D132" t="str">
@@ -4607,10 +4609,10 @@
       <c r="A133" t="str">
         <v>Georgia[p]</v>
       </c>
-      <c r="B133">
+      <c r="B133" s="6">
         <v>3794784</v>
       </c>
-      <c r="C133">
+      <c r="C133" s="6">
         <v>3807492</v>
       </c>
       <c r="D133" t="str">
@@ -4627,10 +4629,10 @@
       <c r="A134" t="str">
         <v>Eritrea</v>
       </c>
-      <c r="B134">
+      <c r="B134" s="6">
         <v>3409447</v>
       </c>
-      <c r="C134">
+      <c r="C134" s="6">
         <v>3470390</v>
       </c>
       <c r="D134" t="str">
@@ -4647,10 +4649,10 @@
       <c r="A135" t="str">
         <v>Mongolia</v>
       </c>
-      <c r="B135">
+      <c r="B135" s="6">
         <v>3386015</v>
       </c>
-      <c r="C135">
+      <c r="C135" s="6">
         <v>3431932</v>
       </c>
       <c r="D135" t="str">
@@ -4667,10 +4669,10 @@
       <c r="A136" t="str">
         <v>Uruguay</v>
       </c>
-      <c r="B136">
+      <c r="B136" s="6">
         <v>3390913</v>
       </c>
-      <c r="C136">
+      <c r="C136" s="6">
         <v>3388081</v>
       </c>
       <c r="D136" t="str">
@@ -4687,10 +4689,10 @@
       <c r="A137" t="str">
         <v>Puerto Rico (United States)</v>
       </c>
-      <c r="B137">
+      <c r="B137" s="6">
         <v>3240968</v>
       </c>
-      <c r="C137">
+      <c r="C137" s="6">
         <v>3242023</v>
       </c>
       <c r="D137" t="str">
@@ -4707,10 +4709,10 @@
       <c r="A138" t="str">
         <v>Bosnia and Herzegovina</v>
       </c>
-      <c r="B138">
+      <c r="B138" s="6">
         <v>3204802</v>
       </c>
-      <c r="C138">
+      <c r="C138" s="6">
         <v>3185073</v>
       </c>
       <c r="D138" t="str">
@@ -4727,10 +4729,10 @@
       <c r="A139" t="str">
         <v>Moldova[q]</v>
       </c>
-      <c r="B139">
+      <c r="B139" s="6">
         <v>3039985</v>
       </c>
-      <c r="C139">
+      <c r="C139" s="6">
         <v>3067070</v>
       </c>
       <c r="D139" t="str">
@@ -4747,10 +4749,10 @@
       <c r="A140" t="str">
         <v>Qatar</v>
       </c>
-      <c r="B140">
+      <c r="B140" s="6">
         <v>2892455</v>
       </c>
-      <c r="C140">
+      <c r="C140" s="6">
         <v>2979082</v>
       </c>
       <c r="D140" t="str">
@@ -4767,10 +4769,10 @@
       <c r="A141" t="str">
         <v>Namibia</v>
       </c>
-      <c r="B141">
+      <c r="B141" s="6">
         <v>2889662</v>
       </c>
-      <c r="C141">
+      <c r="C141" s="6">
         <v>2963095</v>
       </c>
       <c r="D141" t="str">
@@ -4787,10 +4789,10 @@
       <c r="A142" t="str">
         <v>Armenia</v>
       </c>
-      <c r="B142">
+      <c r="B142" s="6">
         <v>2880874</v>
       </c>
-      <c r="C142">
+      <c r="C142" s="6">
         <v>2943393</v>
       </c>
       <c r="D142" t="str">
@@ -4807,10 +4809,10 @@
       <c r="A143" t="str">
         <v>Lithuania</v>
       </c>
-      <c r="B143">
+      <c r="B143" s="6">
         <v>2816919</v>
       </c>
-      <c r="C143">
+      <c r="C143" s="6">
         <v>2854099</v>
       </c>
       <c r="D143" t="str">
@@ -4827,10 +4829,10 @@
       <c r="A144" t="str">
         <v>Jamaica</v>
       </c>
-      <c r="B144">
+      <c r="B144" s="6">
         <v>2839144</v>
       </c>
-      <c r="C144">
+      <c r="C144" s="6">
         <v>2839786</v>
       </c>
       <c r="D144" t="str">
@@ -4847,10 +4849,10 @@
       <c r="A145" t="str">
         <v>Albania</v>
       </c>
-      <c r="B145">
+      <c r="B145" s="6">
         <v>2827608</v>
       </c>
-      <c r="C145">
+      <c r="C145" s="6">
         <v>2811655</v>
       </c>
       <c r="D145" t="str">
@@ -4867,10 +4869,10 @@
       <c r="A146" t="str">
         <v>Gambia</v>
       </c>
-      <c r="B146">
+      <c r="B146" s="6">
         <v>2636470</v>
       </c>
-      <c r="C146">
+      <c r="C146" s="6">
         <v>2697845</v>
       </c>
       <c r="D146" t="str">
@@ -4887,10 +4889,10 @@
       <c r="A147" t="str">
         <v>Gabon</v>
       </c>
-      <c r="B147">
+      <c r="B147" s="6">
         <v>2430747</v>
       </c>
-      <c r="C147">
+      <c r="C147" s="6">
         <v>2484789</v>
       </c>
       <c r="D147" t="str">
@@ -4907,10 +4909,10 @@
       <c r="A148" t="str">
         <v>Botswana</v>
       </c>
-      <c r="B148">
+      <c r="B148" s="6">
         <v>2439892</v>
       </c>
-      <c r="C148">
+      <c r="C148" s="6">
         <v>2480244</v>
       </c>
       <c r="D148" t="str">
@@ -4927,10 +4929,10 @@
       <c r="A149" t="str">
         <v>Lesotho</v>
       </c>
-      <c r="B149">
+      <c r="B149" s="6">
         <v>2286110</v>
       </c>
-      <c r="C149">
+      <c r="C149" s="6">
         <v>2311472</v>
       </c>
       <c r="D149" t="str">
@@ -4947,10 +4949,10 @@
       <c r="A150" t="str">
         <v>Guinea-Bissau</v>
       </c>
-      <c r="B150">
+      <c r="B150" s="6">
         <v>2105529</v>
       </c>
-      <c r="C150">
+      <c r="C150" s="6">
         <v>2153339</v>
       </c>
       <c r="D150" t="str">
@@ -4967,10 +4969,10 @@
       <c r="A151" t="str">
         <v>Slovenia</v>
       </c>
-      <c r="B151">
+      <c r="B151" s="6">
         <v>2115228</v>
       </c>
-      <c r="C151">
+      <c r="C151" s="6">
         <v>2118396</v>
       </c>
       <c r="D151" t="str">
@@ -4987,10 +4989,10 @@
       <c r="A152" t="str">
         <v>Latvia</v>
       </c>
-      <c r="B152">
+      <c r="B152" s="6">
         <v>1881063</v>
       </c>
-      <c r="C152">
+      <c r="C152" s="6">
         <v>1882396</v>
       </c>
       <c r="D152" t="str">
@@ -5007,10 +5009,10 @@
       <c r="A153" t="str">
         <v>Equatorial Guinea</v>
       </c>
-      <c r="B153">
+      <c r="B153" s="6">
         <v>1803545</v>
       </c>
-      <c r="C153">
+      <c r="C153" s="6">
         <v>1847549</v>
       </c>
       <c r="D153" t="str">
@@ -5027,10 +5029,10 @@
       <c r="A154" t="str">
         <v>North Macedonia</v>
       </c>
-      <c r="B154">
+      <c r="B154" s="6">
         <v>1840233</v>
       </c>
-      <c r="C154">
+      <c r="C154" s="6">
         <v>1831802</v>
       </c>
       <c r="D154" t="str">
@@ -5047,10 +5049,10 @@
       <c r="A155" t="str">
         <v>Kosovo[r]</v>
       </c>
-      <c r="B155">
+      <c r="B155" s="6">
         <v>1717946</v>
       </c>
-      <c r="C155">
+      <c r="C155" s="6">
         <v>1700031</v>
       </c>
       <c r="D155" t="str">
@@ -5067,10 +5069,10 @@
       <c r="A156" t="str">
         <v>Bahrain</v>
       </c>
-      <c r="B156">
+      <c r="B156" s="6">
         <v>1533459</v>
       </c>
-      <c r="C156">
+      <c r="C156" s="6">
         <v>1569666</v>
       </c>
       <c r="D156" t="str">
@@ -5087,10 +5089,10 @@
       <c r="A157" t="str">
         <v>Trinidad and Tobago</v>
       </c>
-      <c r="B157">
+      <c r="B157" s="6">
         <v>1495921</v>
       </c>
-      <c r="C157">
+      <c r="C157" s="6">
         <v>1502932</v>
       </c>
       <c r="D157" t="str">
@@ -5107,10 +5109,10 @@
       <c r="A158" t="str">
         <v>Timor-Leste</v>
       </c>
-      <c r="B158">
+      <c r="B158" s="6">
         <v>1369295</v>
       </c>
-      <c r="C158">
+      <c r="C158" s="6">
         <v>1384286</v>
       </c>
       <c r="D158" t="str">
@@ -5127,10 +5129,10 @@
       <c r="A159" t="str">
         <v>Estonia</v>
       </c>
-      <c r="B159">
+      <c r="B159" s="6">
         <v>1350091</v>
       </c>
-      <c r="C159">
+      <c r="C159" s="6">
         <v>1367196</v>
       </c>
       <c r="D159" t="str">
@@ -5147,10 +5149,10 @@
       <c r="A160" t="str">
         <v>Cyprus[s]</v>
       </c>
-      <c r="B160">
+      <c r="B160" s="6">
         <v>1331370</v>
       </c>
-      <c r="C160">
+      <c r="C160" s="6">
         <v>1344976</v>
       </c>
       <c r="D160" t="str">
@@ -5167,10 +5169,10 @@
       <c r="A161" t="str">
         <v>Mauritius</v>
       </c>
-      <c r="B161">
+      <c r="B161" s="6">
         <v>1276130</v>
       </c>
-      <c r="C161">
+      <c r="C161" s="6">
         <v>1273588</v>
       </c>
       <c r="D161" t="str">
@@ -5187,10 +5189,10 @@
       <c r="A162" t="str">
         <v>Eswatini</v>
       </c>
-      <c r="B162">
+      <c r="B162" s="6">
         <v>1218917</v>
       </c>
-      <c r="C162">
+      <c r="C162" s="6">
         <v>1230506</v>
       </c>
       <c r="D162" t="str">
@@ -5207,10 +5209,10 @@
       <c r="A163" t="str">
         <v>Djibouti</v>
       </c>
-      <c r="B163">
+      <c r="B163" s="6">
         <v>1137096</v>
       </c>
-      <c r="C163">
+      <c r="C163" s="6">
         <v>1152944</v>
       </c>
       <c r="D163" t="str">
@@ -5227,10 +5229,10 @@
       <c r="A164" t="str">
         <v>Fiji</v>
       </c>
-      <c r="B164">
+      <c r="B164" s="6">
         <v>919422</v>
       </c>
-      <c r="C164">
+      <c r="C164" s="6">
         <v>924145</v>
       </c>
       <c r="D164" t="str">
@@ -5247,10 +5249,10 @@
       <c r="A165" t="str">
         <v>Réunion (France)</v>
       </c>
-      <c r="B165">
+      <c r="B165" s="6">
         <v>871540</v>
       </c>
-      <c r="C165">
+      <c r="C165" s="6">
         <v>874883</v>
       </c>
       <c r="D165" t="str">
@@ -5267,10 +5269,10 @@
       <c r="A166" t="str">
         <v>Comoros</v>
       </c>
-      <c r="B166">
+      <c r="B166" s="6">
         <v>834188</v>
       </c>
-      <c r="C166">
+      <c r="C166" s="6">
         <v>850387</v>
       </c>
       <c r="D166" t="str">
@@ -5287,10 +5289,10 @@
       <c r="A167" t="str">
         <v>Guyana</v>
       </c>
-      <c r="B167">
+      <c r="B167" s="6">
         <v>821637</v>
       </c>
-      <c r="C167">
+      <c r="C167" s="6">
         <v>826353</v>
       </c>
       <c r="D167" t="str">
@@ -5307,10 +5309,10 @@
       <c r="A168" t="str">
         <v>Solomon Islands</v>
       </c>
-      <c r="B168">
+      <c r="B168" s="6">
         <v>781066</v>
       </c>
-      <c r="C168">
+      <c r="C168" s="6">
         <v>800005</v>
       </c>
       <c r="D168" t="str">
@@ -5327,10 +5329,10 @@
       <c r="A169" t="str">
         <v>Bhutan</v>
       </c>
-      <c r="B169">
+      <c r="B169" s="6">
         <v>780914</v>
       </c>
-      <c r="C169">
+      <c r="C169" s="6">
         <v>786385</v>
       </c>
       <c r="D169" t="str">
@@ -5347,10 +5349,10 @@
       <c r="A170" t="str">
         <v>Macao (China)[t]</v>
       </c>
-      <c r="B170">
+      <c r="B170" s="6">
         <v>704356</v>
       </c>
-      <c r="C170">
+      <c r="C170" s="6">
         <v>713912</v>
       </c>
       <c r="D170" t="str">
@@ -5367,10 +5369,10 @@
       <c r="A171" t="str">
         <v>Luxembourg</v>
       </c>
-      <c r="B171">
+      <c r="B171" s="6">
         <v>653313</v>
       </c>
-      <c r="C171">
+      <c r="C171" s="6">
         <v>665098</v>
       </c>
       <c r="D171" t="str">
@@ -5387,10 +5389,10 @@
       <c r="A172" t="str">
         <v>Montenegro</v>
       </c>
-      <c r="B172">
+      <c r="B172" s="6">
         <v>614648</v>
       </c>
-      <c r="C172">
+      <c r="C172" s="6">
         <v>633552</v>
       </c>
       <c r="D172" t="str">
@@ -5407,10 +5409,10 @@
       <c r="A173" t="str">
         <v>Suriname</v>
       </c>
-      <c r="B173">
+      <c r="B173" s="6">
         <v>623164</v>
       </c>
-      <c r="C173">
+      <c r="C173" s="6">
         <v>628886</v>
       </c>
       <c r="D173" t="str">
@@ -5427,10 +5429,10 @@
       <c r="A174" t="str">
         <v>Western Sahara (disputed)</v>
       </c>
-      <c r="B174">
+      <c r="B174" s="6">
         <v>568739</v>
       </c>
-      <c r="C174">
+      <c r="C174" s="6">
         <v>579729</v>
       </c>
       <c r="D174" t="str">
@@ -5447,10 +5449,10 @@
       <c r="A175" t="str">
         <v>Malta</v>
       </c>
-      <c r="B175">
+      <c r="B175" s="6">
         <v>528192</v>
       </c>
-      <c r="C175">
+      <c r="C175" s="6">
         <v>532956</v>
       </c>
       <c r="D175" t="str">
@@ -5467,10 +5469,10 @@
       <c r="A176" t="str">
         <v>Maldives</v>
       </c>
-      <c r="B176">
+      <c r="B176" s="6">
         <v>524106</v>
       </c>
-      <c r="C176">
+      <c r="C176" s="6">
         <v>525994</v>
       </c>
       <c r="D176" t="str">
@@ -5487,10 +5489,10 @@
       <c r="A177" t="str">
         <v>Cape Verde</v>
       </c>
-      <c r="B177">
+      <c r="B177" s="6">
         <v>519741</v>
       </c>
-      <c r="C177">
+      <c r="C177" s="6">
         <v>522331</v>
       </c>
       <c r="D177" t="str">
@@ -5507,10 +5509,10 @@
       <c r="A178" t="str">
         <v>Brunei</v>
       </c>
-      <c r="B178">
+      <c r="B178" s="6">
         <v>455370</v>
       </c>
-      <c r="C178">
+      <c r="C178" s="6">
         <v>458949</v>
       </c>
       <c r="D178" t="str">
@@ -5527,10 +5529,10 @@
       <c r="A179" t="str">
         <v>Belize</v>
       </c>
-      <c r="B179">
+      <c r="B179" s="6">
         <v>402733</v>
       </c>
-      <c r="C179">
+      <c r="C179" s="6">
         <v>411106</v>
       </c>
       <c r="D179" t="str">
@@ -5547,10 +5549,10 @@
       <c r="A180" t="str">
         <v>Bahamas</v>
       </c>
-      <c r="B180">
+      <c r="B180" s="6">
         <v>397538</v>
       </c>
-      <c r="C180">
+      <c r="C180" s="6">
         <v>399440</v>
       </c>
       <c r="D180" t="str">
@@ -5567,10 +5569,10 @@
       <c r="A181" t="str">
         <v>Iceland</v>
       </c>
-      <c r="B181">
+      <c r="B181" s="6">
         <v>380356</v>
       </c>
-      <c r="C181">
+      <c r="C181" s="6">
         <v>387558</v>
       </c>
       <c r="D181" t="str">
@@ -5587,10 +5589,10 @@
       <c r="A182" t="str">
         <v>Guadeloupe (France)</v>
       </c>
-      <c r="B182">
+      <c r="B182" s="6">
         <v>384697</v>
       </c>
-      <c r="C182">
+      <c r="C182" s="6">
         <v>376517</v>
       </c>
       <c r="D182" t="str">
@@ -5607,10 +5609,10 @@
       <c r="A183" t="str">
         <v>Martinique (France)</v>
       </c>
-      <c r="B183">
+      <c r="B183" s="6">
         <v>349459</v>
       </c>
-      <c r="C183">
+      <c r="C183" s="6">
         <v>346002</v>
       </c>
       <c r="D183" t="str">
@@ -5627,10 +5629,10 @@
       <c r="A184" t="str">
         <v>Vanuatu</v>
       </c>
-      <c r="B184">
+      <c r="B184" s="6">
         <v>313046</v>
       </c>
-      <c r="C184">
+      <c r="C184" s="6">
         <v>320409</v>
       </c>
       <c r="D184" t="str">
@@ -5647,10 +5649,10 @@
       <c r="A185" t="str">
         <v>Mayotte (France)</v>
       </c>
-      <c r="B185">
+      <c r="B185" s="6">
         <v>305269</v>
       </c>
-      <c r="C185">
+      <c r="C185" s="6">
         <v>316015</v>
       </c>
       <c r="D185" t="str">
@@ -5667,10 +5669,10 @@
       <c r="A186" t="str">
         <v>French Guiana (France)</v>
       </c>
-      <c r="B186">
+      <c r="B186" s="6">
         <v>298306</v>
       </c>
-      <c r="C186">
+      <c r="C186" s="6">
         <v>303402</v>
       </c>
       <c r="D186" t="str">
@@ -5687,10 +5689,10 @@
       <c r="A187" t="str">
         <v>New Caledonia (France)</v>
       </c>
-      <c r="B187">
+      <c r="B187" s="6">
         <v>287123</v>
       </c>
-      <c r="C187">
+      <c r="C187" s="6">
         <v>289870</v>
       </c>
       <c r="D187" t="str">
@@ -5707,10 +5709,10 @@
       <c r="A188" t="str">
         <v>Barbados</v>
       </c>
-      <c r="B188">
+      <c r="B188" s="6">
         <v>288318</v>
       </c>
-      <c r="C188">
+      <c r="C188" s="6">
         <v>282336</v>
       </c>
       <c r="D188" t="str">
@@ -5727,10 +5729,10 @@
       <c r="A189" t="str">
         <v>French Polynesia (France)</v>
       </c>
-      <c r="B189">
+      <c r="B189" s="6">
         <v>280378</v>
       </c>
-      <c r="C189">
+      <c r="C189" s="6">
         <v>281118</v>
       </c>
       <c r="D189" t="str">
@@ -5747,10 +5749,10 @@
       <c r="A190" t="str">
         <v>São Tomé and Príncipe</v>
       </c>
-      <c r="B190">
+      <c r="B190" s="6">
         <v>226305</v>
       </c>
-      <c r="C190">
+      <c r="C190" s="6">
         <v>230871</v>
       </c>
       <c r="D190" t="str">
@@ -5767,10 +5769,10 @@
       <c r="A191" t="str">
         <v>Samoa</v>
       </c>
-      <c r="B191">
+      <c r="B191" s="6">
         <v>215261</v>
       </c>
-      <c r="C191">
+      <c r="C191" s="6">
         <v>216663</v>
       </c>
       <c r="D191" t="str">
@@ -5787,10 +5789,10 @@
       <c r="A192" t="str">
         <v>Curaçao (Netherlands)</v>
       </c>
-      <c r="B192">
+      <c r="B192" s="6">
         <v>185345</v>
       </c>
-      <c r="C192">
+      <c r="C192" s="6">
         <v>185427</v>
       </c>
       <c r="D192" t="str">
@@ -5807,10 +5809,10 @@
       <c r="A193" t="str">
         <v>Saint Lucia</v>
       </c>
-      <c r="B193">
+      <c r="B193" s="6">
         <v>178781</v>
       </c>
-      <c r="C193">
+      <c r="C193" s="6">
         <v>179285</v>
       </c>
       <c r="D193" t="str">
@@ -5827,10 +5829,10 @@
       <c r="A194" t="str">
         <v>Guam (United States)</v>
       </c>
-      <c r="B194">
+      <c r="B194" s="6">
         <v>165180</v>
       </c>
-      <c r="C194">
+      <c r="C194" s="6">
         <v>166506</v>
       </c>
       <c r="D194" t="str">
@@ -5847,10 +5849,10 @@
       <c r="A195" t="str">
         <v>Kiribati</v>
       </c>
-      <c r="B195">
+      <c r="B195" s="6">
         <v>130469</v>
       </c>
-      <c r="C195">
+      <c r="C195" s="6">
         <v>132530</v>
       </c>
       <c r="D195" t="str">
@@ -5867,10 +5869,10 @@
       <c r="A196" t="str">
         <v>Seychelles</v>
       </c>
-      <c r="B196">
+      <c r="B196" s="6">
         <v>125522</v>
       </c>
-      <c r="C196">
+      <c r="C196" s="6">
         <v>127951</v>
       </c>
       <c r="D196" t="str">
@@ -5887,10 +5889,10 @@
       <c r="A197" t="str">
         <v>Grenada</v>
       </c>
-      <c r="B197">
+      <c r="B197" s="6">
         <v>116913</v>
       </c>
-      <c r="C197">
+      <c r="C197" s="6">
         <v>117081</v>
       </c>
       <c r="D197" t="str">
@@ -5907,10 +5909,10 @@
       <c r="A198" t="str">
         <v>Federated States of Micronesia</v>
       </c>
-      <c r="B198">
+      <c r="B198" s="6">
         <v>112114</v>
       </c>
-      <c r="C198">
+      <c r="C198" s="6">
         <v>112630</v>
       </c>
       <c r="D198" t="str">
@@ -5927,10 +5929,10 @@
       <c r="A199" t="str">
         <v>Tonga</v>
       </c>
-      <c r="B199">
+      <c r="B199" s="6">
         <v>105042</v>
       </c>
-      <c r="C199">
+      <c r="C199" s="6">
         <v>104597</v>
       </c>
       <c r="D199" t="str">
@@ -5947,10 +5949,10 @@
       <c r="A200" t="str">
         <v>Aruba (Netherlands)</v>
       </c>
-      <c r="B200">
+      <c r="B200" s="6">
         <v>107782</v>
       </c>
-      <c r="C200">
+      <c r="C200" s="6">
         <v>107939</v>
       </c>
       <c r="D200" t="str">
@@ -5967,10 +5969,10 @@
       <c r="A201" t="str">
         <v>Jersey (United Kingdom)</v>
       </c>
-      <c r="B201">
+      <c r="B201" s="6">
         <v>103490</v>
       </c>
-      <c r="C201">
+      <c r="C201" s="6">
         <v>103674</v>
       </c>
       <c r="D201" t="str">
@@ -5987,10 +5989,10 @@
       <c r="A202" t="str">
         <v>Saint Vincent and the Grenadines</v>
       </c>
-      <c r="B202">
+      <c r="B202" s="6">
         <v>102046</v>
       </c>
-      <c r="C202">
+      <c r="C202" s="6">
         <v>101323</v>
       </c>
       <c r="D202" t="str">
@@ -6007,10 +6009,10 @@
       <c r="A203" t="str">
         <v>Antigua and Barbuda</v>
       </c>
-      <c r="B203">
+      <c r="B203" s="6">
         <v>92840</v>
       </c>
-      <c r="C203">
+      <c r="C203" s="6">
         <v>93316</v>
       </c>
       <c r="D203" t="str">
@@ -6027,10 +6029,10 @@
       <c r="A204" t="str">
         <v>U.S. Virgin Islands (United States)</v>
       </c>
-      <c r="B204">
+      <c r="B204" s="6">
         <v>86507</v>
       </c>
-      <c r="C204">
+      <c r="C204" s="6">
         <v>85701</v>
       </c>
       <c r="D204" t="str">
@@ -6047,10 +6049,10 @@
       <c r="A205" t="str">
         <v>Isle of Man (United Kingdom)</v>
       </c>
-      <c r="B205">
+      <c r="B205" s="6">
         <v>84132</v>
       </c>
-      <c r="C205">
+      <c r="C205" s="6">
         <v>84165</v>
       </c>
       <c r="D205" t="str">
@@ -6067,10 +6069,10 @@
       <c r="A206" t="str">
         <v>Andorra</v>
       </c>
-      <c r="B206">
+      <c r="B206" s="6">
         <v>79705</v>
       </c>
-      <c r="C206">
+      <c r="C206" s="6">
         <v>80856</v>
       </c>
       <c r="D206" t="str">
@@ -6087,10 +6089,10 @@
       <c r="A207" t="str">
         <v>Cayman Islands (United Kingdom)</v>
       </c>
-      <c r="B207">
+      <c r="B207" s="6">
         <v>71591</v>
       </c>
-      <c r="C207">
+      <c r="C207" s="6">
         <v>73038</v>
       </c>
       <c r="D207" t="str">
@@ -6107,10 +6109,10 @@
       <c r="A208" t="str">
         <v>Dominica</v>
       </c>
-      <c r="B208">
+      <c r="B208" s="6">
         <v>66826</v>
       </c>
-      <c r="C208">
+      <c r="C208" s="6">
         <v>66510</v>
       </c>
       <c r="D208" t="str">
@@ -6127,10 +6129,10 @@
       <c r="A209" t="str">
         <v>Bermuda (United Kingdom)</v>
       </c>
-      <c r="B209">
+      <c r="B209" s="6">
         <v>64749</v>
       </c>
-      <c r="C209">
+      <c r="C209" s="6">
         <v>64698</v>
       </c>
       <c r="D209" t="str">
@@ -6147,10 +6149,10 @@
       <c r="A210" t="str">
         <v>Guernsey (United Kingdom)</v>
       </c>
-      <c r="B210">
+      <c r="B210" s="6">
         <v>63725</v>
       </c>
-      <c r="C210">
+      <c r="C210" s="6">
         <v>64017</v>
       </c>
       <c r="D210" t="str">
@@ -6167,10 +6169,10 @@
       <c r="A211" t="str">
         <v>Greenland (Denmark)</v>
       </c>
-      <c r="B211">
+      <c r="B211" s="6">
         <v>54990</v>
       </c>
-      <c r="C211">
+      <c r="C211" s="6">
         <v>55922</v>
       </c>
       <c r="D211" t="str">
@@ -6187,10 +6189,10 @@
       <c r="A212" t="str">
         <v>Faroe Islands (Denmark)</v>
       </c>
-      <c r="B212">
+      <c r="B212" s="6">
         <v>54011</v>
       </c>
-      <c r="C212">
+      <c r="C212" s="6">
         <v>54714</v>
       </c>
       <c r="D212" t="str">
@@ -6207,10 +6209,10 @@
       <c r="A213" t="str">
         <v>American Samoa (United States)</v>
       </c>
-      <c r="B213">
+      <c r="B213" s="6">
         <v>48342</v>
       </c>
-      <c r="C213">
+      <c r="C213" s="6">
         <v>47521</v>
       </c>
       <c r="D213" t="str">
@@ -6227,10 +6229,10 @@
       <c r="A214" t="str">
         <v>Saint Kitts and Nevis</v>
       </c>
-      <c r="B214">
+      <c r="B214" s="6">
         <v>46709</v>
       </c>
-      <c r="C214">
+      <c r="C214" s="6">
         <v>46758</v>
       </c>
       <c r="D214" t="str">
@@ -6247,10 +6249,10 @@
       <c r="A215" t="str">
         <v>Turks and Caicos Islands (United Kingdom)</v>
       </c>
-      <c r="B215">
+      <c r="B215" s="6">
         <v>45847</v>
       </c>
-      <c r="C215">
+      <c r="C215" s="6">
         <v>46198</v>
       </c>
       <c r="D215" t="str">
@@ -6267,10 +6269,10 @@
       <c r="A216" t="str">
         <v>Northern Mariana Islands (United States)</v>
       </c>
-      <c r="B216">
+      <c r="B216" s="6">
         <v>46078</v>
       </c>
-      <c r="C216">
+      <c r="C216" s="6">
         <v>45143</v>
       </c>
       <c r="D216" t="str">
@@ -6287,10 +6289,10 @@
       <c r="A217" t="str">
         <v>Sint Maarten (Netherlands)</v>
       </c>
-      <c r="B217">
+      <c r="B217" s="6">
         <v>42139</v>
       </c>
-      <c r="C217">
+      <c r="C217" s="6">
         <v>42749</v>
       </c>
       <c r="D217" t="str">
@@ -6307,10 +6309,10 @@
       <c r="A218" t="str">
         <v>Liechtenstein</v>
       </c>
-      <c r="B218">
+      <c r="B218" s="6">
         <v>39317</v>
       </c>
-      <c r="C218">
+      <c r="C218" s="6">
         <v>39598</v>
       </c>
       <c r="D218" t="str">
@@ -6327,10 +6329,10 @@
       <c r="A219" t="str">
         <v>British Virgin Islands (United Kingdom)</v>
       </c>
-      <c r="B219">
+      <c r="B219" s="6">
         <v>38319</v>
       </c>
-      <c r="C219">
+      <c r="C219" s="6">
         <v>38985</v>
       </c>
       <c r="D219" t="str">
@@ -6347,10 +6349,10 @@
       <c r="A220" t="str">
         <v>Monaco</v>
       </c>
-      <c r="B220">
+      <c r="B220" s="6">
         <v>38931</v>
       </c>
-      <c r="C220">
+      <c r="C220" s="6">
         <v>38956</v>
       </c>
       <c r="D220" t="str">
@@ -6367,10 +6369,10 @@
       <c r="A221" t="str">
         <v>Gibraltar (United Kingdom)</v>
       </c>
-      <c r="B221">
+      <c r="B221" s="6">
         <v>37609</v>
       </c>
-      <c r="C221">
+      <c r="C221" s="6">
         <v>38471</v>
       </c>
       <c r="D221" t="str">
@@ -6387,10 +6389,10 @@
       <c r="A222" t="str">
         <v>Marshall Islands</v>
       </c>
-      <c r="B222">
+      <c r="B222" s="6">
         <v>40077</v>
       </c>
-      <c r="C222">
+      <c r="C222" s="6">
         <v>38827</v>
       </c>
       <c r="D222" t="str">
@@ -6407,10 +6409,10 @@
       <c r="A223" t="str">
         <v>San Marino</v>
       </c>
-      <c r="B223">
+      <c r="B223" s="6">
         <v>34090</v>
       </c>
-      <c r="C223">
+      <c r="C223" s="6">
         <v>33733</v>
       </c>
       <c r="D223" t="str">
@@ -6427,10 +6429,10 @@
       <c r="A224" t="str">
         <v>Caribbean Netherlands (Netherlands)[u]</v>
       </c>
-      <c r="B224">
+      <c r="B224" s="6">
         <v>28627</v>
       </c>
-      <c r="C224">
+      <c r="C224" s="6">
         <v>29898</v>
       </c>
       <c r="D224" t="str">
@@ -6447,10 +6449,10 @@
       <c r="A225" t="str">
         <v>Saint Martin (France)</v>
       </c>
-      <c r="B225">
+      <c r="B225" s="6">
         <v>28870</v>
       </c>
-      <c r="C225">
+      <c r="C225" s="6">
         <v>27515</v>
       </c>
       <c r="D225" t="str">
@@ -6467,10 +6469,10 @@
       <c r="A226" t="str">
         <v>Palau</v>
       </c>
-      <c r="B226">
+      <c r="B226" s="6">
         <v>17759</v>
       </c>
-      <c r="C226">
+      <c r="C226" s="6">
         <v>17727</v>
       </c>
       <c r="D226" t="str">
@@ -6487,10 +6489,10 @@
       <c r="A227" t="str">
         <v>Anguilla (United Kingdom)</v>
       </c>
-      <c r="B227">
+      <c r="B227" s="6">
         <v>14180</v>
       </c>
-      <c r="C227">
+      <c r="C227" s="6">
         <v>14410</v>
       </c>
       <c r="D227" t="str">
@@ -6507,10 +6509,10 @@
       <c r="A228" t="str">
         <v>Cook Islands</v>
       </c>
-      <c r="B228">
+      <c r="B228" s="6">
         <v>14723</v>
       </c>
-      <c r="C228">
+      <c r="C228" s="6">
         <v>14222</v>
       </c>
       <c r="D228" t="str">
@@ -6527,10 +6529,10 @@
       <c r="A229" t="str">
         <v>Nauru</v>
       </c>
-      <c r="B229">
+      <c r="B229" s="6">
         <v>11801</v>
       </c>
-      <c r="C229">
+      <c r="C229" s="6">
         <v>11875</v>
       </c>
       <c r="D229" t="str">
@@ -6547,10 +6549,10 @@
       <c r="A230" t="str">
         <v>Wallis and Futuna (France)</v>
       </c>
-      <c r="B230">
+      <c r="B230" s="6">
         <v>11478</v>
       </c>
-      <c r="C230">
+      <c r="C230" s="6">
         <v>11370</v>
       </c>
       <c r="D230" t="str">
@@ -6567,10 +6569,10 @@
       <c r="A231" t="str">
         <v>Saint Barthélemy (France)</v>
       </c>
-      <c r="B231">
+      <c r="B231" s="6">
         <v>10920</v>
       </c>
-      <c r="C231">
+      <c r="C231" s="6">
         <v>11085</v>
       </c>
       <c r="D231" t="str">
@@ -6587,10 +6589,10 @@
       <c r="A232" t="str">
         <v>Tuvalu</v>
       </c>
-      <c r="B232">
+      <c r="B232" s="6">
         <v>9992</v>
       </c>
-      <c r="C232">
+      <c r="C232" s="6">
         <v>9816</v>
       </c>
       <c r="D232" t="str">
@@ -6607,10 +6609,10 @@
       <c r="A233" t="str">
         <v>Saint Pierre and Miquelon (France)</v>
       </c>
-      <c r="B233">
+      <c r="B233" s="6">
         <v>5732</v>
       </c>
-      <c r="C233">
+      <c r="C233" s="6">
         <v>5681</v>
       </c>
       <c r="D233" t="str">
@@ -6627,10 +6629,10 @@
       <c r="A234" t="str">
         <v>Saint Helena (United Kingdom)[v]</v>
       </c>
-      <c r="B234">
+      <c r="B234" s="6">
         <v>5343</v>
       </c>
-      <c r="C234">
+      <c r="C234" s="6">
         <v>5289</v>
       </c>
       <c r="D234" t="str">
@@ -6647,10 +6649,10 @@
       <c r="A235" t="str">
         <v>Montserrat (United Kingdom)</v>
       </c>
-      <c r="B235">
+      <c r="B235" s="6">
         <v>4453</v>
       </c>
-      <c r="C235">
+      <c r="C235" s="6">
         <v>4420</v>
       </c>
       <c r="D235" t="str">
@@ -6667,10 +6669,10 @@
       <c r="A236" t="str">
         <v>Falkland Islands (United Kingdom)</v>
       </c>
-      <c r="B236">
+      <c r="B236" s="6">
         <v>3490</v>
       </c>
-      <c r="C236">
+      <c r="C236" s="6">
         <v>3477</v>
       </c>
       <c r="D236" t="str">
@@ -6687,10 +6689,10 @@
       <c r="A237" t="str">
         <v>Tokelau (New Zealand)</v>
       </c>
-      <c r="B237">
+      <c r="B237" s="6">
         <v>2290</v>
       </c>
-      <c r="C237">
+      <c r="C237" s="6">
         <v>2397</v>
       </c>
       <c r="D237" t="str">
@@ -6707,10 +6709,10 @@
       <c r="A238" t="str">
         <v>Niue</v>
       </c>
-      <c r="B238">
+      <c r="B238" s="6">
         <v>1821</v>
       </c>
-      <c r="C238">
+      <c r="C238" s="6">
         <v>1817</v>
       </c>
       <c r="D238" t="str">
@@ -6727,10 +6729,10 @@
       <c r="A239" t="str">
         <v>Vatican City[w]</v>
       </c>
-      <c r="B239">
+      <c r="B239" s="6">
         <v>505</v>
       </c>
-      <c r="C239">
+      <c r="C239" s="6">
         <v>496</v>
       </c>
       <c r="D239" t="str">
@@ -6754,14 +6756,14 @@
     <tabColor theme="5" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="A1:E367"/>
-  <sheetFormatPr defaultRowHeight="14.35"/>
+  <sheetFormatPr defaultColWidth="8.734375" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="8.234375" style="3" customWidth="1"/>
-    <col min="2" max="3" width="8.76171875" style="3"/>
-    <col min="4" max="4" width="14.1875" style="3" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.76171875" style="3"/>
-    <col min="6" max="6" width="11.85546875" style="3" bestFit="1" customWidth="1"/>
-    <col min="7" max="16384" width="8.76171875" style="3"/>
+    <col min="1" max="1" width="8.20703125" style="3" customWidth="1"/>
+    <col min="2" max="3" width="8.734375" style="3"/>
+    <col min="4" max="4" width="14.20703125" style="3" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.734375" style="3"/>
+    <col min="6" max="6" width="11.83984375" style="3" bestFit="1" customWidth="1"/>
+    <col min="7" max="16384" width="8.734375" style="3"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -9725,19 +9727,19 @@
     <tabColor theme="9" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="A1:J399"/>
-  <sheetFormatPr defaultRowHeight="20.7"/>
+  <sheetFormatPr defaultColWidth="8.734375" defaultRowHeight="21"/>
   <cols>
-    <col min="1" max="1" width="8.76171875" style="1"/>
-    <col min="2" max="2" width="10.33203125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="8.734375" style="1"/>
+    <col min="2" max="2" width="10.3125" style="1" customWidth="1"/>
     <col min="3" max="3" width="14.5234375" style="1" customWidth="1"/>
-    <col min="4" max="4" width="13.1875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="8.76171875" style="1"/>
-    <col min="6" max="6" width="13.42578125" style="1" customWidth="1"/>
-    <col min="7" max="7" width="13.09375" style="1" customWidth="1"/>
-    <col min="8" max="9" width="8.76171875" style="1"/>
-    <col min="10" max="10" width="15.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.20703125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="8.734375" style="1"/>
+    <col min="6" max="6" width="13.41796875" style="1" customWidth="1"/>
+    <col min="7" max="7" width="13.1015625" style="1" customWidth="1"/>
+    <col min="8" max="9" width="8.734375" style="1"/>
+    <col min="10" max="10" width="15.26171875" style="1" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="8.76171875" style="1"/>
+    <col min="12" max="16384" width="8.734375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
@@ -20114,11 +20116,11 @@
     <tabColor theme="9" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="A1:B7"/>
-  <sheetFormatPr defaultRowHeight="20.7"/>
+  <sheetFormatPr defaultColWidth="8.734375" defaultRowHeight="21"/>
   <cols>
-    <col min="1" max="1" width="19.94921875" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.140625" style="1" customWidth="1"/>
-    <col min="3" max="16384" width="8.76171875" style="1"/>
+    <col min="1" max="1" width="19.9453125" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.15625" style="1" customWidth="1"/>
+    <col min="3" max="16384" width="8.734375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -20190,13 +20192,13 @@
     <tabColor theme="9" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="A1:D15"/>
-  <sheetFormatPr defaultRowHeight="20.7"/>
+  <sheetFormatPr defaultColWidth="8.734375" defaultRowHeight="21"/>
   <cols>
-    <col min="1" max="1" width="24.09375" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="3.140625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="21.76171875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="16384" width="8.76171875" style="1"/>
+    <col min="1" max="1" width="24.1015625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="3.15625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="21.734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="16384" width="8.734375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
